--- a/database/social-workers.xlsx
+++ b/database/social-workers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,9 +479,29 @@
         <v>2025-03-18T06:26:14.853Z</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>WRK004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Anuraj</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Anuraj@worker.com</v>
+      </c>
+      <c r="D5" t="str">
+        <v>kundaraj</v>
+      </c>
+      <c r="E5" t="str">
+        <v>active</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2025-04-11T04:32:27.893Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>